--- a/Data/EXCEL/Transfer/salemon/20240711/2243-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/2243-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F25F728A-D49B-4AF1-9C6C-DA6FC4179279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96B54048-E9AA-46C3-B372-C3237D533361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4570" yWindow="2620" windowWidth="18240" windowHeight="13390" xr2:uid="{E24671C0-AD04-4A2F-A6F1-173FFFF2406F}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{BE76F0CD-26AD-4D96-B9E7-3B48304B796D}"/>
   </bookViews>
   <sheets>
     <sheet name="2243-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,18 +1261,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49405B16-01B8-46CE-8E36-5DFCBFD674A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D7D674-0A8A-418B-A255-23AACADF4C80}">
   <dimension ref="A1:Q175"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1381,7 +1381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>-31.8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>-38.700000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>-34.200000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>-58.8</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>-72.099999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>-1.47</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>-16.8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>-25.3</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>-43.6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>-51.4</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>-45.4</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>-36.200000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>-30.2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>-5.89</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>2838.3</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>5476.3</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>100.6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>-74.400000000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>-86.6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>85.6</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>86.1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>344.7</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>353.2</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>420.2</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>-57.1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>-51.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>-56</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>-50.2</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>-33.200000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>-83.3</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>-85.3</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>-89.3</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>-76.2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>-36.200000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>-31.2</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>-30.6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>-23.5</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>-24.9</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>-38.1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>-25.7</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>-24.1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>-63.2</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>-4.54</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>-2.92</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>-0.83</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>-58.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>-71.7</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5607,7 +5607,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5766,7 +5766,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5819,442 +5819,442 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>42948</v>
       </c>
